--- a/Data app.xlsx
+++ b/Data app.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Planificador02\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1C618AD-3418-417A-AE5E-E7AD313A7E95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40302089-9691-47F4-9B5A-5F64C7634DED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{665D4DEA-18BE-47C2-83D1-361CE9C9EBB8}"/>
   </bookViews>
@@ -826,21 +826,11 @@
       <c r="A12" s="4">
         <v>46153</v>
       </c>
-      <c r="B12" s="1">
-        <v>34256.230000000003</v>
-      </c>
-      <c r="C12" s="1">
-        <v>365.23</v>
-      </c>
-      <c r="D12" s="1">
-        <v>236.65</v>
-      </c>
-      <c r="E12" s="1">
-        <v>36586.519999999997</v>
-      </c>
-      <c r="F12" s="6">
-        <v>4.4800000000000006E-2</v>
-      </c>
+      <c r="B12" s="1"/>
+      <c r="C12" s="1"/>
+      <c r="D12" s="1"/>
+      <c r="E12" s="1"/>
+      <c r="F12" s="6"/>
     </row>
     <row r="13" spans="1:8">
       <c r="A13" s="4">
@@ -944,5 +934,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/Data app.xlsx
+++ b/Data app.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Planificador02\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40302089-9691-47F4-9B5A-5F64C7634DED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76945D97-7D2D-4408-A075-6806C268C708}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{665D4DEA-18BE-47C2-83D1-361CE9C9EBB8}"/>
   </bookViews>
@@ -826,11 +826,21 @@
       <c r="A12" s="4">
         <v>46153</v>
       </c>
-      <c r="B12" s="1"/>
-      <c r="C12" s="1"/>
-      <c r="D12" s="1"/>
-      <c r="E12" s="1"/>
-      <c r="F12" s="6"/>
+      <c r="B12" s="1">
+        <v>27065.47</v>
+      </c>
+      <c r="C12" s="1">
+        <v>817.12</v>
+      </c>
+      <c r="D12" s="1">
+        <v>731.05</v>
+      </c>
+      <c r="E12" s="1">
+        <v>28613.63</v>
+      </c>
+      <c r="F12" s="6">
+        <v>5.4100000000000002E-2</v>
+      </c>
     </row>
     <row r="13" spans="1:8">
       <c r="A13" s="4">

--- a/Data app.xlsx
+++ b/Data app.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Planificador02\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76945D97-7D2D-4408-A075-6806C268C708}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D9B377A-D2D2-428E-B87D-1BDAED0CBA7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{665D4DEA-18BE-47C2-83D1-361CE9C9EBB8}"/>
   </bookViews>
@@ -846,6 +846,21 @@
       <c r="A13" s="4">
         <v>46154</v>
       </c>
+      <c r="B13" s="1">
+        <v>28143.07</v>
+      </c>
+      <c r="C13" s="1">
+        <v>1563.0500000000002</v>
+      </c>
+      <c r="D13" s="1">
+        <v>624.45000000000005</v>
+      </c>
+      <c r="E13" s="1">
+        <v>30330.565000000002</v>
+      </c>
+      <c r="F13" s="6">
+        <v>7.2099999999999997E-2</v>
+      </c>
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="4">

--- a/Data app.xlsx
+++ b/Data app.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Planificador02\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D9B377A-D2D2-428E-B87D-1BDAED0CBA7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B570A89-1216-4ACA-AA40-A8167407A911}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{665D4DEA-18BE-47C2-83D1-361CE9C9EBB8}"/>
   </bookViews>
@@ -79,7 +79,7 @@
     <numFmt numFmtId="44" formatCode="_-&quot;$&quot;* #,##0.00_-;\-&quot;$&quot;* #,##0.00_-;_-&quot;$&quot;* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -101,22 +101,24 @@
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -566,7 +568,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96FD81FD-F679-426D-958A-6FF5D6D0FB85}">
   <dimension ref="A1:H32"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.5546875" style="3"/>
     <col min="2" max="2" width="26.109375" bestFit="1" customWidth="1"/>
@@ -578,7 +580,7 @@
     <col min="8" max="8" width="19.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -604,7 +606,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" s="4">
         <v>46143</v>
       </c>
@@ -630,7 +632,7 @@
         <v>5.31</v>
       </c>
     </row>
-    <row r="3" spans="1:8">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="4">
         <v>46144</v>
       </c>
@@ -656,7 +658,7 @@
         <v>4.72</v>
       </c>
     </row>
-    <row r="4" spans="1:8">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" s="4">
         <v>46145</v>
       </c>
@@ -682,7 +684,7 @@
         <v>2.93</v>
       </c>
     </row>
-    <row r="5" spans="1:8">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" s="4">
         <v>46146</v>
       </c>
@@ -702,7 +704,7 @@
         <v>9.6069801969145593E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:8">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" s="4">
         <v>46147</v>
       </c>
@@ -722,7 +724,7 @@
         <v>6.0855838073872452E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:8">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" s="4">
         <v>46148</v>
       </c>
@@ -742,7 +744,7 @@
         <v>5.8178052138052466E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:8">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" s="4">
         <v>46149</v>
       </c>
@@ -762,7 +764,7 @@
         <v>5.16E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:8">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" s="4">
         <v>46150</v>
       </c>
@@ -782,7 +784,7 @@
         <v>5.5999999999999994E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:8">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" s="4">
         <v>46151</v>
       </c>
@@ -802,7 +804,7 @@
         <v>4.2999999999999997E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:8">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" s="4">
         <v>46152</v>
       </c>
@@ -822,7 +824,7 @@
         <v>4.4500000000000005E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:8">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" s="4">
         <v>46153</v>
       </c>
@@ -842,7 +844,7 @@
         <v>5.4100000000000002E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:8">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" s="4">
         <v>46154</v>
       </c>
@@ -862,97 +864,112 @@
         <v>7.2099999999999997E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:8">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" s="4">
         <v>46155</v>
       </c>
-    </row>
-    <row r="15" spans="1:8">
+      <c r="B14" s="1">
+        <v>32012.239999999998</v>
+      </c>
+      <c r="C14" s="1">
+        <v>1520.23</v>
+      </c>
+      <c r="D14" s="1">
+        <v>540.11</v>
+      </c>
+      <c r="E14" s="1">
+        <v>34072.58</v>
+      </c>
+      <c r="F14" s="6">
+        <v>6.0499999999999998E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" s="4">
         <v>46156</v>
       </c>
     </row>
-    <row r="16" spans="1:8">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" s="4">
         <v>46157</v>
       </c>
     </row>
-    <row r="17" spans="1:1">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17" s="4">
         <v>46158</v>
       </c>
     </row>
-    <row r="18" spans="1:1">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A18" s="4">
         <v>46159</v>
       </c>
     </row>
-    <row r="19" spans="1:1">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A19" s="4">
         <v>46160</v>
       </c>
     </row>
-    <row r="20" spans="1:1">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A20" s="4">
         <v>46161</v>
       </c>
     </row>
-    <row r="21" spans="1:1">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A21" s="4">
         <v>46162</v>
       </c>
     </row>
-    <row r="22" spans="1:1">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A22" s="4">
         <v>46163</v>
       </c>
     </row>
-    <row r="23" spans="1:1">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A23" s="4">
         <v>46164</v>
       </c>
     </row>
-    <row r="24" spans="1:1">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A24" s="4">
         <v>46165</v>
       </c>
     </row>
-    <row r="25" spans="1:1">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A25" s="4">
         <v>46166</v>
       </c>
     </row>
-    <row r="26" spans="1:1">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A26" s="4">
         <v>46167</v>
       </c>
     </row>
-    <row r="27" spans="1:1">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A27" s="4">
         <v>46168</v>
       </c>
     </row>
-    <row r="28" spans="1:1">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A28" s="4">
         <v>46169</v>
       </c>
     </row>
-    <row r="29" spans="1:1">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A29" s="4">
         <v>46170</v>
       </c>
     </row>
-    <row r="30" spans="1:1">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A30" s="4">
         <v>46171</v>
       </c>
     </row>
-    <row r="31" spans="1:1">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A31" s="4">
         <v>46172</v>
       </c>
     </row>
-    <row r="32" spans="1:1">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A32" s="4">
         <v>46173</v>
       </c>

--- a/Data app.xlsx
+++ b/Data app.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Planificador02\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B570A89-1216-4ACA-AA40-A8167407A911}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7F4B8D9-89E4-4C7C-89D3-10AAA12C6D8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{665D4DEA-18BE-47C2-83D1-361CE9C9EBB8}"/>
   </bookViews>
@@ -212,8 +212,12 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="20">
     <cellStyle name="Millares 2" xfId="8" xr:uid="{3F940B62-C413-4377-9601-EE9B66024C04}"/>
@@ -567,17 +571,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96FD81FD-F679-426D-958A-6FF5D6D0FB85}">
-  <dimension ref="A1:H32"/>
+  <dimension ref="A1:I32"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.5546875" style="3"/>
-    <col min="2" max="2" width="26.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="24.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="26.77734375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="27.109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="19.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.33203125" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="24.33203125" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="26.77734375" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="27.109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="19.21875" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.5546875" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
@@ -888,6 +893,21 @@
       <c r="A15" s="4">
         <v>46156</v>
       </c>
+      <c r="B15" s="1">
+        <v>30500.1</v>
+      </c>
+      <c r="C15" s="1">
+        <v>810.24</v>
+      </c>
+      <c r="D15" s="1">
+        <v>675</v>
+      </c>
+      <c r="E15" s="1">
+        <v>31985.34</v>
+      </c>
+      <c r="F15" s="6">
+        <v>4.6399999999999997E-2</v>
+      </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" s="4">

--- a/Data app.xlsx
+++ b/Data app.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Planificador02\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7F4B8D9-89E4-4C7C-89D3-10AAA12C6D8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{214B7F4D-DB00-4E97-8665-07B449B192A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{665D4DEA-18BE-47C2-83D1-361CE9C9EBB8}"/>
   </bookViews>
@@ -913,6 +913,21 @@
       <c r="A16" s="4">
         <v>46157</v>
       </c>
+      <c r="B16" s="1">
+        <v>28804.03</v>
+      </c>
+      <c r="C16" s="1">
+        <v>829.81999999999994</v>
+      </c>
+      <c r="D16" s="1">
+        <v>559.02</v>
+      </c>
+      <c r="E16" s="1">
+        <v>30192.86</v>
+      </c>
+      <c r="F16" s="6">
+        <v>4.5999999999999999E-2</v>
+      </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17" s="4">

--- a/Data app.xlsx
+++ b/Data app.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Planificador02\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{214B7F4D-DB00-4E97-8665-07B449B192A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42DE367F-81FB-4581-B2D0-A3CE97254667}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{665D4DEA-18BE-47C2-83D1-361CE9C9EBB8}"/>
   </bookViews>
@@ -79,7 +79,7 @@
     <numFmt numFmtId="44" formatCode="_-&quot;$&quot;* #,##0.00_-;\-&quot;$&quot;* #,##0.00_-;_-&quot;$&quot;* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -120,6 +120,13 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -138,7 +145,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="20">
+  <cellStyleXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
       <alignment vertical="center"/>
@@ -197,8 +204,9 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -212,14 +220,11 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="20" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="20">
+  <cellStyles count="21">
     <cellStyle name="Millares 2" xfId="8" xr:uid="{3F940B62-C413-4377-9601-EE9B66024C04}"/>
     <cellStyle name="Millares 3" xfId="12" xr:uid="{03B2F211-1EED-48AF-9FEF-ABB3D9B43A3B}"/>
     <cellStyle name="Millares 4" xfId="17" xr:uid="{0EC25592-58AB-4C5D-9AB5-3FE2073323D7}"/>
@@ -235,6 +240,7 @@
     <cellStyle name="Normal 3 3" xfId="19" xr:uid="{3CECAF2A-482E-4DF7-BB9A-BAE4EFF65258}"/>
     <cellStyle name="Normal 4" xfId="4" xr:uid="{EB9EC252-F9C6-4CAC-9208-D95BEFA1DFE7}"/>
     <cellStyle name="Normal 5" xfId="5" xr:uid="{CF751A03-074A-4A17-AFD2-9C3087BB90E9}"/>
+    <cellStyle name="Porcentaje" xfId="20" builtinId="5"/>
     <cellStyle name="Porcentaje 2" xfId="2" xr:uid="{A6060016-C167-4ABB-B064-4A9607201CC3}"/>
     <cellStyle name="Porcentaje 2 2" xfId="7" xr:uid="{02411173-DF3F-40F5-BC78-AB01F274B4A8}"/>
     <cellStyle name="Porcentaje 2 3" xfId="16" xr:uid="{061D9D32-9672-4E03-987C-6BDE70BD3845}"/>
@@ -579,7 +585,7 @@
     <col min="3" max="3" width="27.33203125" style="2" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="24.33203125" style="2" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="26.77734375" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.109375" style="5" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="27.109375" style="2" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="19.21875" style="2" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="11.5546875" style="2"/>
@@ -601,7 +607,7 @@
       <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="5" t="s">
         <v>5</v>
       </c>
       <c r="G1" s="2" t="s">
@@ -653,7 +659,7 @@
       <c r="E3" s="1">
         <v>21214.420000000002</v>
       </c>
-      <c r="F3" s="6">
+      <c r="F3" s="5">
         <v>8.7778972981585157E-2</v>
       </c>
       <c r="G3" s="2" t="s">
@@ -679,7 +685,7 @@
       <c r="E4" s="1">
         <v>24154.68</v>
       </c>
-      <c r="F4" s="6">
+      <c r="F4" s="5">
         <v>5.9674978099482162E-2</v>
       </c>
       <c r="G4" s="2" t="s">
@@ -705,7 +711,7 @@
       <c r="E5" s="1">
         <v>21499.68</v>
       </c>
-      <c r="F5" s="6">
+      <c r="F5" s="5">
         <v>9.6069801969145593E-2</v>
       </c>
     </row>
@@ -725,7 +731,7 @@
       <c r="E6" s="1">
         <v>23887.93</v>
       </c>
-      <c r="F6" s="6">
+      <c r="F6" s="5">
         <v>6.0855838073872452E-2</v>
       </c>
     </row>
@@ -745,7 +751,7 @@
       <c r="E7" s="1">
         <v>25693.71</v>
       </c>
-      <c r="F7" s="6">
+      <c r="F7" s="5">
         <v>5.8178052138052466E-2</v>
       </c>
     </row>
@@ -765,7 +771,7 @@
       <c r="E8" s="1">
         <v>28854</v>
       </c>
-      <c r="F8" s="6">
+      <c r="F8" s="5">
         <v>5.16E-2</v>
       </c>
     </row>
@@ -785,7 +791,7 @@
       <c r="E9" s="1">
         <v>32841.15</v>
       </c>
-      <c r="F9" s="6">
+      <c r="F9" s="5">
         <v>5.5999999999999994E-2</v>
       </c>
     </row>
@@ -805,7 +811,7 @@
       <c r="E10" s="1">
         <v>33055.230000000003</v>
       </c>
-      <c r="F10" s="6">
+      <c r="F10" s="5">
         <v>4.2999999999999997E-2</v>
       </c>
     </row>
@@ -825,7 +831,7 @@
       <c r="E11" s="1">
         <v>25342.22</v>
       </c>
-      <c r="F11" s="6">
+      <c r="F11" s="5">
         <v>4.4500000000000005E-2</v>
       </c>
     </row>
@@ -845,7 +851,7 @@
       <c r="E12" s="1">
         <v>28613.63</v>
       </c>
-      <c r="F12" s="6">
+      <c r="F12" s="5">
         <v>5.4100000000000002E-2</v>
       </c>
     </row>
@@ -865,7 +871,7 @@
       <c r="E13" s="1">
         <v>30330.565000000002</v>
       </c>
-      <c r="F13" s="6">
+      <c r="F13" s="5">
         <v>7.2099999999999997E-2</v>
       </c>
     </row>
@@ -885,7 +891,7 @@
       <c r="E14" s="1">
         <v>34072.58</v>
       </c>
-      <c r="F14" s="6">
+      <c r="F14" s="5">
         <v>6.0499999999999998E-2</v>
       </c>
     </row>
@@ -905,7 +911,7 @@
       <c r="E15" s="1">
         <v>31985.34</v>
       </c>
-      <c r="F15" s="6">
+      <c r="F15" s="5">
         <v>4.6399999999999997E-2</v>
       </c>
     </row>
@@ -925,86 +931,116 @@
       <c r="E16" s="1">
         <v>30192.86</v>
       </c>
-      <c r="F16" s="6">
+      <c r="F16" s="5">
         <v>4.5999999999999999E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" s="4">
         <v>46158</v>
       </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B17" s="1">
+        <v>26778.880000000001</v>
+      </c>
+      <c r="C17" s="1">
+        <v>1148.3500000000001</v>
+      </c>
+      <c r="D17" s="1">
+        <v>747.1</v>
+      </c>
+      <c r="E17" s="1">
+        <v>28674.33</v>
+      </c>
+      <c r="F17" s="5">
+        <v>6.6100000000000006E-2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" s="4">
         <v>46159</v>
       </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B18" s="1">
+        <v>27621.239999999998</v>
+      </c>
+      <c r="C18" s="1">
+        <v>1085.46</v>
+      </c>
+      <c r="D18" s="1">
+        <v>482.88</v>
+      </c>
+      <c r="E18" s="1">
+        <v>29189.57</v>
+      </c>
+      <c r="F18" s="5">
+        <v>5.3699999999999998E-2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" s="4">
         <v>46160</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" s="4">
         <v>46161</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" s="4">
         <v>46162</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" s="4">
         <v>46163</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" s="4">
         <v>46164</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" s="4">
         <v>46165</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" s="4">
         <v>46166</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" s="4">
         <v>46167</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" s="4">
         <v>46168</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" s="4">
         <v>46169</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29" s="4">
         <v>46170</v>
       </c>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30" s="4">
         <v>46171</v>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31" s="4">
         <v>46172</v>
       </c>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32" s="4">
         <v>46173</v>
       </c>
